--- a/רפק.xlsx
+++ b/רפק.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Sachar\חוליית פיתוח\2. פיתוחים ואפיונים חיצוניים במחלקת שכר וגמלאות\חוברת שכר דיגיטלית 2026\תוצאות סופי\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hila_n\Desktop\חוברת שכר 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47E79CA-E985-4097-9A0E-09F1433C672A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2635447C-9299-4C80-A42D-96AE4A440B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="1740" windowWidth="15915" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1665" yWindow="3630" windowWidth="13485" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="15">
   <si>
     <t>ותק</t>
   </si>
@@ -79,9 +82,6 @@
   </si>
   <si>
     <t>סה"כ משכורת ברוטו</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תוספת לאחר שנה </t>
   </si>
 </sst>
 </file>
@@ -679,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -690,7 +690,7 @@
     <col min="7" max="7" width="11.75" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
@@ -712,11 +712,8 @@
       <c r="G1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
@@ -738,11 +735,8 @@
       <c r="G2" s="8">
         <v>11138.140000000001</v>
       </c>
-      <c r="H2" s="9">
-        <v>836.22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>7</v>
       </c>
@@ -764,11 +758,8 @@
       <c r="G3" s="9">
         <v>12096.710000000001</v>
       </c>
-      <c r="H3" s="9">
-        <v>864.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>7</v>
       </c>
@@ -790,11 +781,8 @@
       <c r="G4" s="9">
         <v>13055.290000000003</v>
       </c>
-      <c r="H4" s="9">
-        <v>892.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>7</v>
       </c>
@@ -816,11 +804,8 @@
       <c r="G5" s="9">
         <v>11329.040000000003</v>
       </c>
-      <c r="H5" s="9">
-        <v>841.87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
@@ -842,11 +827,8 @@
       <c r="G6" s="9">
         <v>12287.630000000003</v>
       </c>
-      <c r="H6" s="9">
-        <v>870.26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -868,11 +850,8 @@
       <c r="G7" s="10">
         <v>13246.200000000003</v>
       </c>
-      <c r="H7" s="9">
-        <v>898.64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>6</v>
       </c>
@@ -894,11 +873,8 @@
       <c r="G8" s="8">
         <v>10480.85</v>
       </c>
-      <c r="H8" s="9">
-        <v>825.85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
@@ -920,11 +896,8 @@
       <c r="G9" s="9">
         <v>11487.179999999998</v>
       </c>
-      <c r="H9" s="9">
-        <v>855.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
@@ -946,11 +919,8 @@
       <c r="G10" s="9">
         <v>12493.5</v>
       </c>
-      <c r="H10" s="9">
-        <v>885.45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>6</v>
       </c>
@@ -972,11 +942,8 @@
       <c r="G11" s="9">
         <v>10664.670000000002</v>
       </c>
-      <c r="H11" s="9">
-        <v>831.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>6</v>
       </c>
@@ -998,11 +965,8 @@
       <c r="G12" s="9">
         <v>11671</v>
       </c>
-      <c r="H12" s="9">
-        <v>861.08999999999992</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>6</v>
       </c>
@@ -1024,11 +988,8 @@
       <c r="G13" s="10">
         <v>12677.32</v>
       </c>
-      <c r="H13" s="9">
-        <v>890.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>9</v>
       </c>
@@ -1050,11 +1011,8 @@
       <c r="G14" s="8">
         <v>12118.92</v>
       </c>
-      <c r="H14" s="9">
-        <v>855.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>9</v>
       </c>
@@ -1076,11 +1034,8 @@
       <c r="G15" s="9">
         <v>13144.070000000003</v>
       </c>
-      <c r="H15" s="9">
-        <v>886.11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>9</v>
       </c>
@@ -1102,11 +1057,8 @@
       <c r="G16" s="9">
         <v>14169.240000000002</v>
       </c>
-      <c r="H16" s="9">
-        <v>916.47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>9</v>
       </c>
@@ -1128,11 +1080,8 @@
       <c r="G17" s="9">
         <v>12323.080000000004</v>
       </c>
-      <c r="H17" s="9">
-        <v>861.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>9</v>
       </c>
@@ -1154,11 +1103,8 @@
       <c r="G18" s="9">
         <v>13348.24</v>
       </c>
-      <c r="H18" s="9">
-        <v>892.15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>9</v>
       </c>
@@ -1180,11 +1126,8 @@
       <c r="G19" s="10">
         <v>14373.41</v>
       </c>
-      <c r="H19" s="9">
-        <v>922.51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>8</v>
       </c>
@@ -1206,11 +1149,8 @@
       <c r="G20" s="8">
         <v>13095.36</v>
       </c>
-      <c r="H20" s="9">
-        <v>887.77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>8</v>
       </c>
@@ -1232,11 +1172,8 @@
       <c r="G21" s="9">
         <v>14229.65</v>
       </c>
-      <c r="H21" s="9">
-        <v>921.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>8</v>
       </c>
@@ -1258,11 +1195,8 @@
       <c r="G22" s="9">
         <v>15363.95</v>
       </c>
-      <c r="H22" s="9">
-        <v>954.94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>8</v>
       </c>
@@ -1284,11 +1218,8 @@
       <c r="G23" s="9">
         <v>13321.26</v>
       </c>
-      <c r="H23" s="9">
-        <v>894.45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>8</v>
       </c>
@@ -1310,11 +1241,8 @@
       <c r="G24" s="9">
         <v>14455.550000000001</v>
       </c>
-      <c r="H24" s="9">
-        <v>928.04</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>8</v>
       </c>
@@ -1336,17 +1264,14 @@
       <c r="G25" s="10">
         <v>15589.82</v>
       </c>
-      <c r="H25" s="9">
-        <v>961.63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
